--- a/CV/Lightweight/assets/IR_SR_Lightweight_Result.xlsx
+++ b/CV/Lightweight/assets/IR_SR_Lightweight_Result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13640" firstSheet="8" activeTab="10"/>
+    <workbookView windowWidth="27660" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="SR" sheetId="2" r:id="rId1"/>
@@ -261,8 +261,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -414,12 +422,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -808,76 +828,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,10 +900,10 @@
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -898,10 +912,10 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -910,10 +924,10 @@
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -922,10 +936,10 @@
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -934,11 +948,17 @@
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -988,6 +1008,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2021,7 +2053,7 @@
       <c r="B5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>356</v>
       </c>
       <c r="D5" s="16" t="s">
@@ -2151,7 +2183,7 @@
       <c r="B6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <v>266</v>
       </c>
       <c r="D6" s="16">
@@ -2815,10 +2847,10 @@
         <v>99.9</v>
       </c>
       <c r="R11" s="2"/>
-      <c r="S11" s="2">
+      <c r="S11" s="19">
         <v>34.62</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="19">
         <v>0.9292</v>
       </c>
       <c r="U11" s="2">
@@ -2897,115 +2929,115 @@
       <c r="BB11" s="2"/>
     </row>
     <row r="12" spans="1:54">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="19">
         <v>393</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19">
         <v>38.24</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="19">
         <v>0.9619</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="19">
         <v>34.08</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="19">
         <v>0.9215</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="19">
         <v>32.35</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="19">
         <v>0.9026</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="19">
         <v>32.99</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="19">
         <v>0.9354</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="19">
         <v>39.4</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="19">
         <v>0.9786</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="19">
         <v>399</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2">
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19">
         <v>34.69</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" s="19">
         <v>0.93</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12" s="19">
         <v>30.65</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12" s="19">
         <v>0.8477</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="19">
         <v>29.28</v>
       </c>
-      <c r="X12" s="2">
+      <c r="X12" s="19">
         <v>0.8117</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" s="19">
         <v>28.9</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z12" s="19">
         <v>0.8659</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AA12" s="19">
         <v>34.31</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AB12" s="19">
         <v>0.9487</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" s="19">
         <v>408</v>
       </c>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2">
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19">
         <v>32.53</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AG12" s="19">
         <v>0.8994</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AH12" s="19">
         <v>28.88</v>
       </c>
-      <c r="AI12" s="2">
+      <c r="AI12" s="19">
         <v>0.7876</v>
       </c>
-      <c r="AJ12" s="2">
+      <c r="AJ12" s="19">
         <v>27.76</v>
       </c>
-      <c r="AK12" s="2">
+      <c r="AK12" s="19">
         <v>0.744</v>
       </c>
-      <c r="AL12" s="2">
+      <c r="AL12" s="19">
         <v>26.69</v>
       </c>
-      <c r="AM12" s="2">
+      <c r="AM12" s="19">
         <v>0.8025</v>
       </c>
-      <c r="AN12" s="2">
+      <c r="AN12" s="19">
         <v>31.24</v>
       </c>
-      <c r="AO12" s="2">
+      <c r="AO12" s="19">
         <v>0.9148</v>
       </c>
       <c r="AP12" s="2"/>
@@ -3073,10 +3105,10 @@
         <v>77.3</v>
       </c>
       <c r="R13" s="2"/>
-      <c r="S13" s="2">
+      <c r="S13" s="19">
         <v>34.63</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13" s="19">
         <v>0.929</v>
       </c>
       <c r="U13" s="2">
@@ -3110,10 +3142,10 @@
         <v>42.1</v>
       </c>
       <c r="AE13" s="2"/>
-      <c r="AF13" s="2">
+      <c r="AF13" s="19">
         <v>32.56</v>
       </c>
-      <c r="AG13" s="2">
+      <c r="AG13" s="19">
         <v>0.8992</v>
       </c>
       <c r="AH13" s="2">
@@ -3161,7 +3193,7 @@
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="19">
         <v>387</v>
       </c>
       <c r="D14" s="2"/>
@@ -3424,7 +3456,7 @@
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="19">
         <v>298</v>
       </c>
       <c r="D16" s="2"/>
@@ -3545,10 +3577,10 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2">
+      <c r="F17" s="19">
         <v>38.32</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="20">
         <v>0.9618</v>
       </c>
       <c r="H17" s="2">
@@ -3576,10 +3608,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="2">
+      <c r="S17" s="19">
         <v>34.84</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17" s="20">
         <v>0.9307</v>
       </c>
       <c r="U17" s="2">
@@ -3609,10 +3641,10 @@
       <c r="AE17" s="2">
         <v>40.7</v>
       </c>
-      <c r="AF17" s="2">
+      <c r="AF17" s="19">
         <v>32.57</v>
       </c>
-      <c r="AG17" s="2">
+      <c r="AG17" s="19">
         <v>0.899</v>
       </c>
       <c r="AH17" s="2">
